--- a/type_split_data_1981_2006.xlsx
+++ b/type_split_data_1981_2006.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/TEP4290-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C94EF1-49A5-AF4F-81B0-1ED30EF53822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CF6BF3-700F-D845-B6F9-975E259149B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
